--- a/pin_config.xlsx
+++ b/pin_config.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12800"/>
+    <workbookView windowWidth="30240" windowHeight="12800" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="241">
   <si>
     <t>ph0</t>
   </si>
@@ -705,6 +706,51 @@
   </si>
   <si>
     <t>is_pc_on</t>
+  </si>
+  <si>
+    <t>PAC1</t>
+  </si>
+  <si>
+    <t>K4_drv</t>
+  </si>
+  <si>
+    <t>PAC2</t>
+  </si>
+  <si>
+    <t>K5_drv</t>
+  </si>
+  <si>
+    <t>PAC3</t>
+  </si>
+  <si>
+    <t>K7_drv</t>
+  </si>
+  <si>
+    <t>PAC4</t>
+  </si>
+  <si>
+    <t>PAC6</t>
+  </si>
+  <si>
+    <t>PDC1</t>
+  </si>
+  <si>
+    <t>PDC2</t>
+  </si>
+  <si>
+    <t>PDC3</t>
+  </si>
+  <si>
+    <t>PDC4</t>
+  </si>
+  <si>
+    <t>PDC5</t>
+  </si>
+  <si>
+    <t>PDC6</t>
+  </si>
+  <si>
+    <t>PDC7</t>
   </si>
 </sst>
 </file>
@@ -1850,7 +1896,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="23.9230769230769" style="1" customWidth="1"/>
@@ -2859,34 +2905,29 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" t="s">
-        <v>193</v>
-      </c>
-      <c r="B95" t="s">
-        <v>194</v>
-      </c>
-      <c r="C95" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" t="s">
-        <v>195</v>
-      </c>
-      <c r="B96" t="s">
-        <v>196</v>
-      </c>
-      <c r="C96" t="s">
-        <v>11</v>
-      </c>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>175</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C94" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96"/>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B97" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C97" t="s">
         <v>11</v>
@@ -2894,10 +2935,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B98" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
@@ -2905,10 +2946,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B99" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
@@ -2916,57 +2957,57 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B100" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C100" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B101" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C101" t="s">
-        <v>4</v>
-      </c>
-      <c r="D101" t="s">
-        <v>207</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B102" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C102" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B103" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C103" t="s">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="D103" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B104" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C104" t="s">
         <v>11</v>
@@ -2974,10 +3015,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B105" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C105" t="s">
         <v>11</v>
@@ -2985,32 +3026,32 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B106" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C106" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B107" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C107" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B108" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C108" t="s">
         <v>4</v>
@@ -3018,10 +3059,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B109" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C109" t="s">
         <v>4</v>
@@ -3029,13 +3070,143 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
+        <v>220</v>
+      </c>
+      <c r="B110" t="s">
+        <v>221</v>
+      </c>
+      <c r="C110" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>222</v>
+      </c>
+      <c r="B111" t="s">
+        <v>223</v>
+      </c>
+      <c r="C111" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
         <v>224</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B112" t="s">
         <v>225</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C112" t="s">
         <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="1"/>
+  <cols>
+    <col min="2" max="2" width="10.8461538461538" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/pin_config.xlsx
+++ b/pin_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12800" activeTab="1"/>
+    <workbookView windowWidth="30240" windowHeight="12800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="251">
   <si>
     <t>ph0</t>
   </si>
@@ -195,6 +195,12 @@
     <t>eth_mdio</t>
   </si>
   <si>
+    <t xml:space="preserve">pa7 </t>
+  </si>
+  <si>
+    <t>eth_crs_dv</t>
+  </si>
+  <si>
     <t>pa8</t>
   </si>
   <si>
@@ -294,6 +300,12 @@
     <t>k13_en</t>
   </si>
   <si>
+    <t>pb10</t>
+  </si>
+  <si>
+    <t>eth_rx_er</t>
+  </si>
+  <si>
     <t>pb12</t>
   </si>
   <si>
@@ -318,12 +330,6 @@
     <t>can2_rx</t>
   </si>
   <si>
-    <t>pb10</t>
-  </si>
-  <si>
-    <t>eth_rx_er</t>
-  </si>
-  <si>
     <t>pb13</t>
   </si>
   <si>
@@ -366,6 +372,24 @@
     <t>adc3_inp12</t>
   </si>
   <si>
+    <t>pc1</t>
+  </si>
+  <si>
+    <t>eth_mdc</t>
+  </si>
+  <si>
+    <t>pc4</t>
+  </si>
+  <si>
+    <t>eth_rxd0</t>
+  </si>
+  <si>
+    <t>pc5</t>
+  </si>
+  <si>
+    <t>eth_rxd1</t>
+  </si>
+  <si>
     <t>pc6</t>
   </si>
   <si>
@@ -429,24 +453,6 @@
     <t>adc3_inp1</t>
   </si>
   <si>
-    <t>pc1</t>
-  </si>
-  <si>
-    <t>eth_mdc</t>
-  </si>
-  <si>
-    <t>pc4</t>
-  </si>
-  <si>
-    <t>eth_rxd0</t>
-  </si>
-  <si>
-    <t>pc5</t>
-  </si>
-  <si>
-    <t>eth_rxd1</t>
-  </si>
-  <si>
     <t>pd0</t>
   </si>
   <si>
@@ -706,6 +712,30 @@
   </si>
   <si>
     <t>is_pc_on</t>
+  </si>
+  <si>
+    <t>pg10</t>
+  </si>
+  <si>
+    <t>phy_led1</t>
+  </si>
+  <si>
+    <t>pg11</t>
+  </si>
+  <si>
+    <t>eth_tx_en</t>
+  </si>
+  <si>
+    <t>pg12</t>
+  </si>
+  <si>
+    <t>eth_txd1</t>
+  </si>
+  <si>
+    <t>pg13</t>
+  </si>
+  <si>
+    <t>eth_txd0</t>
   </si>
   <si>
     <t>PAC1</t>
@@ -1896,7 +1926,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="23.9230769230769" style="1" customWidth="1"/>
@@ -2162,15 +2192,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>55</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C25" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2206,71 +2233,71 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" t="s">
         <v>66</v>
-      </c>
-      <c r="B30" t="s">
-        <v>67</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>69</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
         <v>70</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>72</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>73</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" t="s">
         <v>7</v>
       </c>
-      <c r="D32" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="D33" t="s">
         <v>76</v>
       </c>
-      <c r="C33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -2278,49 +2305,49 @@
         <v>78</v>
       </c>
       <c r="C34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" t="s">
         <v>7</v>
       </c>
-      <c r="D34" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>80</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="D35" t="s">
         <v>81</v>
-      </c>
-      <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
         <v>83</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
       </c>
       <c r="D37" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>86</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
         <v>87</v>
-      </c>
-      <c r="C38" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2331,18 +2358,15 @@
         <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>90</v>
       </c>
       <c r="B40" t="s">
         <v>91</v>
-      </c>
-      <c r="C40" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2353,7 +2377,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2386,15 +2410,15 @@
         <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C45" t="s">
         <v>4</v>
@@ -2402,10 +2426,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
         <v>4</v>
@@ -2413,115 +2437,95 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>104</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B48" t="s">
         <v>105</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>106</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C48" t="s">
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
         <v>7</v>
       </c>
-      <c r="D48" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>109</v>
-      </c>
-      <c r="B49" s="1" t="s">
+      <c r="D51" t="s">
         <v>110</v>
       </c>
-      <c r="C49" t="s">
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" t="s">
         <v>7</v>
       </c>
-      <c r="D49" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>112</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="D52" t="s">
         <v>113</v>
       </c>
-      <c r="C50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
         <v>114</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B53" t="s">
         <v>115</v>
       </c>
-      <c r="C51" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
         <v>116</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B54" t="s">
         <v>117</v>
       </c>
-      <c r="C52" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
         <v>118</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B55" t="s">
         <v>119</v>
-      </c>
-      <c r="C53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>120</v>
-      </c>
-      <c r="B54" t="s">
-        <v>121</v>
-      </c>
-      <c r="C54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C56" t="s">
         <v>11</v>
@@ -2529,60 +2533,54 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
         <v>126</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B59" t="s">
         <v>127</v>
       </c>
-      <c r="C57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
-        <v>128</v>
-      </c>
-      <c r="B58" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>131</v>
-      </c>
-      <c r="B59" t="s">
-        <v>73</v>
-      </c>
       <c r="C59" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" t="s">
-        <v>132</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C60" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
@@ -2590,27 +2588,60 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="2:2">
-      <c r="B63"/>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64"/>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>134</v>
+      </c>
+      <c r="B63" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>139</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="B66" t="s">
+        <v>115</v>
       </c>
       <c r="C66" t="s">
         <v>4</v>
@@ -2618,65 +2649,38 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>140</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>141</v>
+        <v>116</v>
+      </c>
+      <c r="B67" t="s">
+        <v>117</v>
       </c>
       <c r="C67" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>144</v>
-      </c>
-      <c r="B69" t="s">
-        <v>145</v>
-      </c>
-      <c r="C69" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" t="s">
-        <v>147</v>
-      </c>
-      <c r="C70" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
-        <v>148</v>
-      </c>
-      <c r="B71" t="s">
-        <v>149</v>
-      </c>
-      <c r="C71" t="s">
-        <v>4</v>
-      </c>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70"/>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>150</v>
-      </c>
-      <c r="B72" t="s">
-        <v>151</v>
+        <v>141</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C72" t="s">
         <v>4</v>
@@ -2684,10 +2688,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>152</v>
-      </c>
-      <c r="B73" t="s">
-        <v>153</v>
+        <v>142</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="C73" t="s">
         <v>4</v>
@@ -2695,10 +2699,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
         <v>4</v>
@@ -2706,10 +2710,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B75" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C75" t="s">
         <v>4</v>
@@ -2717,10 +2721,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C76" t="s">
         <v>4</v>
@@ -2728,10 +2732,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>160</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>161</v>
+        <v>150</v>
+      </c>
+      <c r="B77" t="s">
+        <v>151</v>
       </c>
       <c r="C77" t="s">
         <v>4</v>
@@ -2739,46 +2743,54 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>162</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
+      </c>
+      <c r="B78" t="s">
+        <v>153</v>
       </c>
       <c r="C78" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>164</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
+      </c>
+      <c r="B79" t="s">
+        <v>155</v>
       </c>
       <c r="C79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>166</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
+      </c>
+      <c r="B80" t="s">
+        <v>157</v>
       </c>
       <c r="C80" t="s">
         <v>4</v>
       </c>
-      <c r="D80" t="s">
-        <v>168</v>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C82" t="s">
         <v>4</v>
@@ -2786,10 +2798,10 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>171</v>
-      </c>
-      <c r="B83" t="s">
-        <v>172</v>
+        <v>162</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="C83" t="s">
         <v>4</v>
@@ -2797,54 +2809,46 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>173</v>
-      </c>
-      <c r="B84" t="s">
-        <v>174</v>
+        <v>164</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="C84" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>175</v>
-      </c>
-      <c r="B85" t="s">
-        <v>176</v>
+        <v>166</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="C85" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>177</v>
-      </c>
-      <c r="B86" t="s">
-        <v>178</v>
+        <v>168</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="C86" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" t="s">
-        <v>179</v>
-      </c>
-      <c r="B87" t="s">
-        <v>180</v>
-      </c>
-      <c r="C87" t="s">
-        <v>4</v>
+      <c r="D86" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C88" t="s">
         <v>4</v>
@@ -2852,10 +2856,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C89" t="s">
         <v>4</v>
@@ -2863,10 +2867,10 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C90" t="s">
         <v>4</v>
@@ -2874,10 +2878,10 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B91" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C91" t="s">
         <v>4</v>
@@ -2885,10 +2889,10 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B92" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C92" t="s">
         <v>4</v>
@@ -2896,10 +2900,10 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C93" t="s">
         <v>4</v>
@@ -2907,107 +2911,104 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>175</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
+      </c>
+      <c r="B94" t="s">
+        <v>184</v>
       </c>
       <c r="C94" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="2:2">
-      <c r="B95"/>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96"/>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>185</v>
+      </c>
+      <c r="B95" t="s">
+        <v>186</v>
+      </c>
+      <c r="C95" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>187</v>
+      </c>
+      <c r="B96" t="s">
+        <v>188</v>
+      </c>
+      <c r="C96" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B97" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C97" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B98" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C98" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B99" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C99" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>199</v>
-      </c>
-      <c r="B100" t="s">
-        <v>200</v>
+        <v>177</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="C100" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101"/>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102"/>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>195</v>
+      </c>
+      <c r="B103" t="s">
+        <v>196</v>
+      </c>
+      <c r="C103" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" t="s">
-        <v>201</v>
-      </c>
-      <c r="B101" t="s">
-        <v>202</v>
-      </c>
-      <c r="C101" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" t="s">
-        <v>203</v>
-      </c>
-      <c r="B102" t="s">
-        <v>204</v>
-      </c>
-      <c r="C102" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" t="s">
-        <v>205</v>
-      </c>
-      <c r="B103" t="s">
-        <v>206</v>
-      </c>
-      <c r="C103" t="s">
-        <v>4</v>
-      </c>
-      <c r="D103" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B104" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C104" t="s">
         <v>11</v>
@@ -3015,10 +3016,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C105" t="s">
         <v>11</v>
@@ -3026,10 +3027,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B106" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C106" t="s">
         <v>11</v>
@@ -3037,10 +3038,10 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B107" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C107" t="s">
         <v>11</v>
@@ -3048,57 +3049,158 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B108" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C108" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B109" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C109" t="s">
         <v>4</v>
+      </c>
+      <c r="D109" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B110" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C110" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B111" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C111" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B112" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C112" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>216</v>
+      </c>
+      <c r="B113" t="s">
+        <v>217</v>
+      </c>
+      <c r="C113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>218</v>
+      </c>
+      <c r="B114" t="s">
+        <v>219</v>
+      </c>
+      <c r="C114" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>220</v>
+      </c>
+      <c r="B115" t="s">
+        <v>221</v>
+      </c>
+      <c r="C115" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>222</v>
+      </c>
+      <c r="B116" t="s">
+        <v>223</v>
+      </c>
+      <c r="C116" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>224</v>
+      </c>
+      <c r="B117" t="s">
+        <v>225</v>
+      </c>
+      <c r="C117" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>226</v>
+      </c>
+      <c r="B118" t="s">
+        <v>227</v>
+      </c>
+      <c r="C118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>228</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>230</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>232</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>234</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3118,95 +3220,95 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
